--- a/Lista de compras.xlsx
+++ b/Lista de compras.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Aulas\5. Projetos TIC - Química - 232\ptic232-quimica\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Aulas\5. Projetos TIC - Química - 232\ptic232\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B27494D2-E1C0-4B28-94C2-380DAC6C3796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98EFC246-A2CF-4E09-BEE6-12221A498ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8560CDDB-73D0-445B-B9C1-C7905941B13A}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8560CDDB-73D0-445B-B9C1-C7905941B13A}"/>
   </bookViews>
   <sheets>
     <sheet name="Lista" sheetId="1" r:id="rId1"/>
@@ -123,10 +123,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -252,21 +250,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -391,6 +374,17 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -408,7 +402,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -417,37 +411,85 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="4" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="44" fontId="8" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="14" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -456,44 +498,19 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -502,46 +519,11 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -867,7 +849,7 @@
     <col min="1" max="1" width="10.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="31" style="1" customWidth="1"/>
     <col min="3" max="3" width="20.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" style="1" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="20.140625" style="2" customWidth="1"/>
     <col min="7" max="7" width="19.5703125" style="2" customWidth="1"/>
@@ -876,223 +858,337 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
     </row>
     <row r="2" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="22"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="39">
+      <c r="A2" s="8"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="19">
         <v>0.05</v>
       </c>
-      <c r="G2" s="25">
+      <c r="G2" s="11">
         <v>0.05</v>
       </c>
-      <c r="H2" s="41" t="s">
+      <c r="H2" s="21" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="40" t="s">
+      <c r="F3" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="40" t="s">
+      <c r="H3" s="20" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="3" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="31">
         <v>16.79</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="32">
         <v>1</v>
       </c>
-      <c r="E4" s="10"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="29"/>
+      <c r="E4" s="31">
+        <f>C4*D4</f>
+        <v>16.79</v>
+      </c>
+      <c r="F4" s="31">
+        <f>E4*0.95</f>
+        <v>15.950499999999998</v>
+      </c>
+      <c r="G4" s="31">
+        <f>E4*1.05</f>
+        <v>17.6295</v>
+      </c>
+      <c r="H4" s="33">
+        <f>(E4*1.1)/3</f>
+        <v>6.1563333333333334</v>
+      </c>
     </row>
     <row r="5" spans="1:8" s="3" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="7">
         <v>8.5500000000000007</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="35">
         <v>3</v>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="29"/>
+      <c r="E5" s="7">
+        <f t="shared" ref="E5:E11" si="0">C5*D5</f>
+        <v>25.650000000000002</v>
+      </c>
+      <c r="F5" s="7">
+        <f t="shared" ref="F5:F11" si="1">E5*0.95</f>
+        <v>24.3675</v>
+      </c>
+      <c r="G5" s="7">
+        <f t="shared" ref="G5:G11" si="2">E5*1.05</f>
+        <v>26.932500000000005</v>
+      </c>
+      <c r="H5" s="13">
+        <f t="shared" ref="H5:H11" si="3">(E5*1.1)/3</f>
+        <v>9.4050000000000011</v>
+      </c>
     </row>
     <row r="6" spans="1:8" s="3" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <v>20.99</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="35">
         <v>1</v>
       </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="29"/>
+      <c r="E6" s="7">
+        <f t="shared" si="0"/>
+        <v>20.99</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="1"/>
+        <v>19.940499999999997</v>
+      </c>
+      <c r="G6" s="7">
+        <f t="shared" si="2"/>
+        <v>22.0395</v>
+      </c>
+      <c r="H6" s="13">
+        <f t="shared" si="3"/>
+        <v>7.6963333333333326</v>
+      </c>
     </row>
     <row r="7" spans="1:8" s="3" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="7">
         <v>3.29</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="35">
         <v>2</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="29"/>
+      <c r="E7" s="7">
+        <f t="shared" si="0"/>
+        <v>6.58</v>
+      </c>
+      <c r="F7" s="7">
+        <f t="shared" si="1"/>
+        <v>6.2509999999999994</v>
+      </c>
+      <c r="G7" s="7">
+        <f t="shared" si="2"/>
+        <v>6.9090000000000007</v>
+      </c>
+      <c r="H7" s="13">
+        <f t="shared" si="3"/>
+        <v>2.412666666666667</v>
+      </c>
     </row>
     <row r="8" spans="1:8" s="3" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="7">
         <v>5.43</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="35">
         <v>6</v>
       </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="29"/>
+      <c r="E8" s="7">
+        <f t="shared" si="0"/>
+        <v>32.58</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="1"/>
+        <v>30.950999999999997</v>
+      </c>
+      <c r="G8" s="7">
+        <f t="shared" si="2"/>
+        <v>34.209000000000003</v>
+      </c>
+      <c r="H8" s="13">
+        <f t="shared" si="3"/>
+        <v>11.946</v>
+      </c>
     </row>
     <row r="9" spans="1:8" s="3" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="7">
         <v>7.25</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="35">
         <v>2</v>
       </c>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="29"/>
+      <c r="E9" s="7">
+        <f t="shared" si="0"/>
+        <v>14.5</v>
+      </c>
+      <c r="F9" s="7">
+        <f t="shared" si="1"/>
+        <v>13.774999999999999</v>
+      </c>
+      <c r="G9" s="7">
+        <f t="shared" si="2"/>
+        <v>15.225000000000001</v>
+      </c>
+      <c r="H9" s="13">
+        <f t="shared" si="3"/>
+        <v>5.3166666666666673</v>
+      </c>
     </row>
     <row r="10" spans="1:8" s="3" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="7">
         <v>5.4</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="35">
         <v>3</v>
       </c>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="29"/>
+      <c r="E10" s="7">
+        <f t="shared" si="0"/>
+        <v>16.200000000000003</v>
+      </c>
+      <c r="F10" s="7">
+        <f t="shared" si="1"/>
+        <v>15.390000000000002</v>
+      </c>
+      <c r="G10" s="7">
+        <f t="shared" si="2"/>
+        <v>17.010000000000005</v>
+      </c>
+      <c r="H10" s="13">
+        <f t="shared" si="3"/>
+        <v>5.9400000000000013</v>
+      </c>
     </row>
     <row r="11" spans="1:8" s="3" customFormat="1" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="32" t="s">
+      <c r="B11" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="36">
+      <c r="C11" s="17">
         <v>2.58</v>
       </c>
-      <c r="D11" s="33">
+      <c r="D11" s="16">
         <v>6</v>
       </c>
-      <c r="E11" s="34"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="37"/>
+      <c r="E11" s="17">
+        <f t="shared" si="0"/>
+        <v>15.48</v>
+      </c>
+      <c r="F11" s="17">
+        <f t="shared" si="1"/>
+        <v>14.706</v>
+      </c>
+      <c r="G11" s="17">
+        <f t="shared" si="2"/>
+        <v>16.254000000000001</v>
+      </c>
+      <c r="H11" s="18">
+        <f t="shared" si="3"/>
+        <v>5.676000000000001</v>
+      </c>
     </row>
     <row r="12" spans="1:8" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
     </row>
     <row r="13" spans="1:8" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="38"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="37">
+        <f>SUM(C4:C11)</f>
+        <v>70.28</v>
+      </c>
+      <c r="D13" s="36">
+        <f t="shared" ref="D13:H13" si="4">SUM(D4:D11)</f>
+        <v>24</v>
+      </c>
+      <c r="E13" s="37">
+        <f t="shared" si="4"/>
+        <v>148.76999999999998</v>
+      </c>
+      <c r="F13" s="37">
+        <f t="shared" si="4"/>
+        <v>141.33150000000001</v>
+      </c>
+      <c r="G13" s="37">
+        <f t="shared" si="4"/>
+        <v>156.20849999999999</v>
+      </c>
+      <c r="H13" s="37">
+        <f t="shared" si="4"/>
+        <v>54.549000000000007</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
